--- a/docs/gantt.xlsx
+++ b/docs/gantt.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EA03AC4-D6FD-49BE-8188-C0682D4D717D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8D46FD-EA8B-4A04-A265-7BCA313A4DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Гантт" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
   <si>
     <t>План проекта (Гантт) · пары 5–30 · магазин обуви</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>Бычкова Полина, Сотникова Диана</t>
+  </si>
+  <si>
+    <t>готово</t>
   </si>
 </sst>
 </file>
@@ -207,7 +210,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -222,6 +225,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -253,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -265,13 +274,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -584,22 +594,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -631,8 +641,8 @@
       <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>48</v>
+      <c r="E5" s="10" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -648,8 +658,8 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" t="s">
-        <v>10</v>
+      <c r="E6" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -843,7 +853,7 @@
       <c r="A19" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="5" t="s">
         <v>49</v>
       </c>
     </row>
